--- a/artfynd/A 20269-2024 artfynd.xlsx
+++ b/artfynd/A 20269-2024 artfynd.xlsx
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117446539</v>
+        <v>117456480</v>
       </c>
       <c r="B6" t="n">
-        <v>91962</v>
+        <v>97836</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,41 +1138,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493954</v>
+        <v>494066</v>
       </c>
       <c r="R6" t="n">
-        <v>6936641</v>
+        <v>6936666</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,49 +1211,40 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117456588</v>
+        <v>117446539</v>
       </c>
       <c r="B7" t="n">
-        <v>78480</v>
+        <v>91962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,40 +1257,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493818</v>
+        <v>493954</v>
       </c>
       <c r="R7" t="n">
-        <v>6936682</v>
+        <v>6936641</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,40 +1314,49 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117456480</v>
+        <v>117456588</v>
       </c>
       <c r="B8" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,39 +1365,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494066</v>
+        <v>493818</v>
       </c>
       <c r="R8" t="n">
-        <v>6936666</v>
+        <v>6936682</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -4632,10 +4632,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117451854</v>
+        <v>117449164</v>
       </c>
       <c r="B37" t="n">
-        <v>97836</v>
+        <v>78125</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4644,42 +4644,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494197</v>
+        <v>494158</v>
       </c>
       <c r="R37" t="n">
-        <v>6936819</v>
+        <v>6936645</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4711,7 +4707,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4721,7 +4717,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4736,22 +4732,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117449164</v>
+        <v>117451854</v>
       </c>
       <c r="B38" t="n">
-        <v>78125</v>
+        <v>97836</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4760,38 +4756,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494158</v>
+        <v>494197</v>
       </c>
       <c r="R38" t="n">
-        <v>6936645</v>
+        <v>6936819</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4848,12 +4848,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5320,10 +5320,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117456705</v>
+        <v>117449604</v>
       </c>
       <c r="B43" t="n">
-        <v>97836</v>
+        <v>79098</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5332,50 +5332,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493873</v>
+        <v>494163</v>
       </c>
       <c r="R43" t="n">
-        <v>6936630</v>
+        <v>6936647</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5405,18 +5393,27 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5435,10 +5432,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117449604</v>
+        <v>117456705</v>
       </c>
       <c r="B44" t="n">
-        <v>79098</v>
+        <v>97836</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5447,38 +5444,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494163</v>
+        <v>493873</v>
       </c>
       <c r="R44" t="n">
-        <v>6936647</v>
+        <v>6936630</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5508,27 +5517,18 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20269-2024 artfynd.xlsx
+++ b/artfynd/A 20269-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117450152</v>
+        <v>117456588</v>
       </c>
       <c r="B2" t="n">
-        <v>77412</v>
+        <v>78480</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494270</v>
+        <v>493818</v>
       </c>
       <c r="R2" t="n">
-        <v>6936698</v>
+        <v>6936682</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,27 +751,18 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117451670</v>
+        <v>117450148</v>
       </c>
       <c r="B3" t="n">
-        <v>90648</v>
+        <v>77412</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>6487</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494179</v>
+        <v>494266</v>
       </c>
       <c r="R3" t="n">
-        <v>6936869</v>
+        <v>6936694</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +881,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117451261</v>
+        <v>117445529</v>
       </c>
       <c r="B4" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,37 +909,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494261</v>
+        <v>493855</v>
       </c>
       <c r="R4" t="n">
-        <v>6936695</v>
+        <v>6936651</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +993,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117456809</v>
+        <v>117449658</v>
       </c>
       <c r="B5" t="n">
-        <v>97836</v>
+        <v>79098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,50 +1017,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493939</v>
+        <v>494111</v>
       </c>
       <c r="R5" t="n">
-        <v>6936608</v>
+        <v>6936636</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,37 +1078,46 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117456480</v>
+        <v>117448263</v>
       </c>
       <c r="B6" t="n">
         <v>97836</v>
@@ -1159,29 +1150,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494066</v>
+        <v>493988</v>
       </c>
       <c r="R6" t="n">
-        <v>6936666</v>
+        <v>6936610</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,40 +1190,49 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117446539</v>
+        <v>117456705</v>
       </c>
       <c r="B7" t="n">
-        <v>91962</v>
+        <v>97836</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,41 +1241,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493954</v>
+        <v>493873</v>
       </c>
       <c r="R7" t="n">
-        <v>6936641</v>
+        <v>6936630</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,49 +1314,40 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117456588</v>
+        <v>117448979</v>
       </c>
       <c r="B8" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,37 +1360,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493818</v>
+        <v>494103</v>
       </c>
       <c r="R8" t="n">
-        <v>6936682</v>
+        <v>6936656</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,18 +1417,27 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1574,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117445529</v>
+        <v>117453471</v>
       </c>
       <c r="B10" t="n">
-        <v>78480</v>
+        <v>79521</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1586,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493855</v>
+        <v>493905</v>
       </c>
       <c r="R10" t="n">
         <v>6936651</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1649,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117446108</v>
+        <v>117451454</v>
       </c>
       <c r="B11" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,41 +1695,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493925</v>
+        <v>494251</v>
       </c>
       <c r="R11" t="n">
-        <v>6936640</v>
+        <v>6936767</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1761,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1771,12 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Fem plantor</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117456532</v>
+        <v>117453528</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>78736</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1815,53 +1807,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6459</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493986</v>
+        <v>493910</v>
       </c>
       <c r="R12" t="n">
-        <v>6936667</v>
+        <v>6936649</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1888,40 +1868,49 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117453438</v>
+        <v>117448702</v>
       </c>
       <c r="B13" t="n">
-        <v>97836</v>
+        <v>57287</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1930,41 +1919,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493899</v>
+        <v>493988</v>
       </c>
       <c r="R13" t="n">
-        <v>6936634</v>
+        <v>6936610</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1993,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2003,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,22 +2012,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117448263</v>
+        <v>117451276</v>
       </c>
       <c r="B14" t="n">
-        <v>97836</v>
+        <v>79098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2042,41 +2036,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493988</v>
+        <v>494282</v>
       </c>
       <c r="R14" t="n">
-        <v>6936610</v>
+        <v>6936738</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2105,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2115,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,22 +2124,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117445550</v>
+        <v>117450152</v>
       </c>
       <c r="B15" t="n">
-        <v>97836</v>
+        <v>77412</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2154,41 +2148,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493843</v>
+        <v>494270</v>
       </c>
       <c r="R15" t="n">
-        <v>6936660</v>
+        <v>6936698</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2217,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2227,12 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>15 plantor</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,22 +2236,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117445404</v>
+        <v>117447632</v>
       </c>
       <c r="B16" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2271,41 +2260,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493855</v>
+        <v>493952</v>
       </c>
       <c r="R16" t="n">
-        <v>6936651</v>
+        <v>6936643</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2334,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2344,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,22 +2348,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117453471</v>
+        <v>117449164</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>78125</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2383,41 +2372,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493905</v>
+        <v>494158</v>
       </c>
       <c r="R17" t="n">
-        <v>6936651</v>
+        <v>6936645</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2446,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2456,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,22 +2460,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117448990</v>
+        <v>117449588</v>
       </c>
       <c r="B18" t="n">
-        <v>78217</v>
+        <v>78125</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2499,21 +2488,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2523,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494108</v>
+        <v>494111</v>
       </c>
       <c r="R18" t="n">
-        <v>6936658</v>
+        <v>6936636</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2568,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,22 +2572,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117456740</v>
+        <v>117451261</v>
       </c>
       <c r="B19" t="n">
-        <v>95384</v>
+        <v>79098</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2611,38 +2600,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493943</v>
+        <v>494261</v>
       </c>
       <c r="R19" t="n">
-        <v>6936625</v>
+        <v>6936695</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2672,18 +2657,27 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2702,10 +2696,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117447462</v>
+        <v>117451640</v>
       </c>
       <c r="B20" t="n">
-        <v>78480</v>
+        <v>90648</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2714,41 +2708,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493958</v>
+        <v>494172</v>
       </c>
       <c r="R20" t="n">
-        <v>6936638</v>
+        <v>6936859</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2777,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2781,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,10 +2808,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117453528</v>
+        <v>117453438</v>
       </c>
       <c r="B21" t="n">
-        <v>78736</v>
+        <v>97836</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2826,25 +2820,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6459</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2854,13 +2848,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493910</v>
+        <v>493899</v>
       </c>
       <c r="R21" t="n">
-        <v>6936649</v>
+        <v>6936634</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2889,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2899,7 +2893,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117453330</v>
+        <v>117448932</v>
       </c>
       <c r="B22" t="n">
-        <v>79561</v>
+        <v>78480</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2942,46 +2936,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494077</v>
+        <v>494095</v>
       </c>
       <c r="R22" t="n">
-        <v>6936703</v>
+        <v>6936663</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3010,7 +2995,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3005,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,19 +3020,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117445657</v>
+        <v>117445550</v>
       </c>
       <c r="B23" t="n">
         <v>97836</v>
@@ -3080,29 +3065,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493851</v>
+        <v>493843</v>
       </c>
       <c r="R23" t="n">
-        <v>6936645</v>
+        <v>6936660</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3131,7 +3107,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3141,7 +3117,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>15 plantor</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,22 +3137,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117446238</v>
+        <v>117449528</v>
       </c>
       <c r="B24" t="n">
-        <v>95384</v>
+        <v>78125</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3184,37 +3165,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493934</v>
+        <v>494173</v>
       </c>
       <c r="R24" t="n">
-        <v>6936628</v>
+        <v>6936639</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3243,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3253,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3280,10 +3261,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117448805</v>
+        <v>117445404</v>
       </c>
       <c r="B25" t="n">
-        <v>57287</v>
+        <v>97836</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3292,46 +3273,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493988</v>
+        <v>493855</v>
       </c>
       <c r="R25" t="n">
-        <v>6936610</v>
+        <v>6936651</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3360,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3370,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3385,22 +3361,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117451454</v>
+        <v>117456809</v>
       </c>
       <c r="B26" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3409,38 +3385,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>494251</v>
+        <v>493939</v>
       </c>
       <c r="R26" t="n">
-        <v>6936767</v>
+        <v>6936608</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3470,49 +3458,40 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117448932</v>
+        <v>117448964</v>
       </c>
       <c r="B27" t="n">
-        <v>78480</v>
+        <v>57440</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3525,21 +3504,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3549,10 +3528,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494095</v>
+        <v>494104</v>
       </c>
       <c r="R27" t="n">
-        <v>6936663</v>
+        <v>6936645</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3621,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117449658</v>
+        <v>117456509</v>
       </c>
       <c r="B28" t="n">
-        <v>79098</v>
+        <v>97836</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3633,38 +3612,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494111</v>
+        <v>494062</v>
       </c>
       <c r="R28" t="n">
-        <v>6936636</v>
+        <v>6936661</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3694,49 +3685,40 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117447632</v>
+        <v>117451670</v>
       </c>
       <c r="B29" t="n">
-        <v>78480</v>
+        <v>90648</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3745,38 +3727,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493952</v>
+        <v>494179</v>
       </c>
       <c r="R29" t="n">
-        <v>6936643</v>
+        <v>6936869</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3808,7 +3790,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3818,7 +3800,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3833,22 +3815,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117451328</v>
+        <v>117456740</v>
       </c>
       <c r="B30" t="n">
-        <v>78480</v>
+        <v>95384</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3861,34 +3843,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494269</v>
+        <v>493943</v>
       </c>
       <c r="R30" t="n">
-        <v>6936706</v>
+        <v>6936625</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3918,27 +3904,18 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3957,10 +3934,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117453136</v>
+        <v>117453330</v>
       </c>
       <c r="B31" t="n">
-        <v>90464</v>
+        <v>79561</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3969,41 +3946,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494041</v>
+        <v>494077</v>
       </c>
       <c r="R31" t="n">
-        <v>6936700</v>
+        <v>6936703</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4032,7 +4018,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4042,7 +4028,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4057,22 +4043,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117449980</v>
+        <v>117447462</v>
       </c>
       <c r="B32" t="n">
-        <v>78514</v>
+        <v>78480</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4085,37 +4071,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>494241</v>
+        <v>493958</v>
       </c>
       <c r="R32" t="n">
-        <v>6936727</v>
+        <v>6936638</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4144,7 +4130,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4154,7 +4140,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4169,22 +4155,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117451640</v>
+        <v>117445657</v>
       </c>
       <c r="B33" t="n">
-        <v>90648</v>
+        <v>97836</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4197,37 +4183,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494172</v>
+        <v>493851</v>
       </c>
       <c r="R33" t="n">
-        <v>6936859</v>
+        <v>6936645</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4256,7 +4251,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4266,7 +4261,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4281,22 +4276,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117451276</v>
+        <v>117448190</v>
       </c>
       <c r="B34" t="n">
-        <v>79098</v>
+        <v>80437</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4309,21 +4304,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4333,13 +4328,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494282</v>
+        <v>494007</v>
       </c>
       <c r="R34" t="n">
-        <v>6936738</v>
+        <v>6936619</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4368,7 +4363,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4378,7 +4373,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4405,10 +4400,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117448964</v>
+        <v>117448990</v>
       </c>
       <c r="B35" t="n">
-        <v>57440</v>
+        <v>78217</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4421,21 +4416,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4445,10 +4440,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494104</v>
+        <v>494108</v>
       </c>
       <c r="R35" t="n">
-        <v>6936645</v>
+        <v>6936658</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4517,7 +4512,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117456450</v>
+        <v>117456550</v>
       </c>
       <c r="B36" t="n">
         <v>97836</v>
@@ -4552,7 +4547,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4569,10 +4564,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494064</v>
+        <v>493924</v>
       </c>
       <c r="R36" t="n">
-        <v>6936712</v>
+        <v>6936635</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4632,10 +4627,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117449164</v>
+        <v>117448642</v>
       </c>
       <c r="B37" t="n">
-        <v>78125</v>
+        <v>78514</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4648,34 +4643,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>494158</v>
+        <v>493988</v>
       </c>
       <c r="R37" t="n">
-        <v>6936645</v>
+        <v>6936610</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4707,7 +4702,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4717,7 +4712,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4732,19 +4727,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117451854</v>
+        <v>117446108</v>
       </c>
       <c r="B38" t="n">
         <v>97836</v>
@@ -4777,24 +4772,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494197</v>
+        <v>493925</v>
       </c>
       <c r="R38" t="n">
-        <v>6936819</v>
+        <v>6936640</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4823,7 +4814,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4833,7 +4824,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Fem plantor</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4848,22 +4844,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117449588</v>
+        <v>117449604</v>
       </c>
       <c r="B39" t="n">
-        <v>78125</v>
+        <v>79098</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4876,21 +4872,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4900,10 +4896,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494111</v>
+        <v>494163</v>
       </c>
       <c r="R39" t="n">
-        <v>6936636</v>
+        <v>6936647</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4935,7 +4931,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4945,7 +4941,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4960,22 +4956,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117456550</v>
+        <v>117453136</v>
       </c>
       <c r="B40" t="n">
-        <v>97836</v>
+        <v>90464</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4984,50 +4980,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493924</v>
+        <v>494041</v>
       </c>
       <c r="R40" t="n">
-        <v>6936635</v>
+        <v>6936700</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5057,40 +5041,49 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117453657</v>
+        <v>117449980</v>
       </c>
       <c r="B41" t="n">
-        <v>97836</v>
+        <v>78514</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5099,47 +5092,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493910</v>
+        <v>494241</v>
       </c>
       <c r="R41" t="n">
-        <v>6936651</v>
+        <v>6936727</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5171,7 +5155,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5181,7 +5165,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5196,22 +5180,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117448642</v>
+        <v>117456450</v>
       </c>
       <c r="B42" t="n">
-        <v>78514</v>
+        <v>97836</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5220,38 +5204,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493988</v>
+        <v>494064</v>
       </c>
       <c r="R42" t="n">
-        <v>6936610</v>
+        <v>6936712</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5281,49 +5277,40 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117449604</v>
+        <v>117456532</v>
       </c>
       <c r="B43" t="n">
-        <v>79098</v>
+        <v>97836</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5332,38 +5319,50 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>494163</v>
+        <v>493986</v>
       </c>
       <c r="R43" t="n">
-        <v>6936647</v>
+        <v>6936667</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5393,27 +5392,18 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5432,7 +5422,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117456705</v>
+        <v>117456679</v>
       </c>
       <c r="B44" t="n">
         <v>97836</v>
@@ -5467,7 +5457,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5484,10 +5474,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493873</v>
+        <v>493840</v>
       </c>
       <c r="R44" t="n">
-        <v>6936630</v>
+        <v>6936658</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5547,10 +5537,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117450148</v>
+        <v>117451854</v>
       </c>
       <c r="B45" t="n">
-        <v>77412</v>
+        <v>97836</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5559,38 +5549,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494266</v>
+        <v>494197</v>
       </c>
       <c r="R45" t="n">
-        <v>6936694</v>
+        <v>6936819</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5622,7 +5616,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5632,7 +5626,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5647,19 +5641,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117456679</v>
+        <v>117453657</v>
       </c>
       <c r="B46" t="n">
         <v>97836</v>
@@ -5694,7 +5688,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5702,19 +5696,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493840</v>
+        <v>493910</v>
       </c>
       <c r="R46" t="n">
-        <v>6936658</v>
+        <v>6936651</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5744,40 +5735,49 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117448979</v>
+        <v>117451328</v>
       </c>
       <c r="B47" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5790,21 +5790,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494103</v>
+        <v>494269</v>
       </c>
       <c r="R47" t="n">
-        <v>6936656</v>
+        <v>6936706</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5886,10 +5886,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117448190</v>
+        <v>117446238</v>
       </c>
       <c r="B48" t="n">
-        <v>80437</v>
+        <v>95384</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5902,34 +5902,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1049</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>494007</v>
+        <v>493934</v>
       </c>
       <c r="R48" t="n">
-        <v>6936619</v>
+        <v>6936628</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5998,10 +5998,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117449528</v>
+        <v>117446539</v>
       </c>
       <c r="B49" t="n">
-        <v>78125</v>
+        <v>91962</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6014,21 +6014,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6038,13 +6038,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>494173</v>
+        <v>493954</v>
       </c>
       <c r="R49" t="n">
-        <v>6936639</v>
+        <v>6936641</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6110,7 +6110,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117456509</v>
+        <v>117456480</v>
       </c>
       <c r="B50" t="n">
         <v>97836</v>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494062</v>
+        <v>494066</v>
       </c>
       <c r="R50" t="n">
-        <v>6936661</v>
+        <v>6936666</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6332,10 +6332,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117506039</v>
+        <v>117505814</v>
       </c>
       <c r="B52" t="n">
-        <v>79561</v>
+        <v>95384</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6348,26 +6348,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6375,13 +6376,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493988</v>
+        <v>493952</v>
       </c>
       <c r="R52" t="n">
-        <v>6936642</v>
+        <v>6936632</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6438,10 +6439,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117506518</v>
+        <v>117506039</v>
       </c>
       <c r="B53" t="n">
-        <v>79098</v>
+        <v>79561</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6454,21 +6455,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6481,13 +6482,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494188</v>
+        <v>493988</v>
       </c>
       <c r="R53" t="n">
-        <v>6936650</v>
+        <v>6936642</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6544,10 +6545,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117506348</v>
+        <v>117506518</v>
       </c>
       <c r="B54" t="n">
-        <v>90648</v>
+        <v>79098</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6556,25 +6557,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6587,10 +6588,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494153</v>
+        <v>494188</v>
       </c>
       <c r="R54" t="n">
-        <v>6936771</v>
+        <v>6936650</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6650,10 +6651,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117505814</v>
+        <v>117506348</v>
       </c>
       <c r="B55" t="n">
-        <v>95384</v>
+        <v>90648</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6662,31 +6663,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>1503</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6694,10 +6694,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493952</v>
+        <v>494153</v>
       </c>
       <c r="R55" t="n">
-        <v>6936632</v>
+        <v>6936771</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 20269-2024 artfynd.xlsx
+++ b/artfynd/A 20269-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117456588</v>
+        <v>117456740</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>95386</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493818</v>
+        <v>493943</v>
       </c>
       <c r="R2" t="n">
-        <v>6936682</v>
+        <v>6936625</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117450148</v>
+        <v>117451261</v>
       </c>
       <c r="B3" t="n">
-        <v>77412</v>
+        <v>79100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494266</v>
+        <v>494261</v>
       </c>
       <c r="R3" t="n">
-        <v>6936694</v>
+        <v>6936695</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,22 +882,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117445529</v>
+        <v>117449528</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>78127</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,37 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493855</v>
+        <v>494173</v>
       </c>
       <c r="R4" t="n">
-        <v>6936651</v>
+        <v>6936639</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117449658</v>
+        <v>117447632</v>
       </c>
       <c r="B5" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,34 +1022,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494111</v>
+        <v>493952</v>
       </c>
       <c r="R5" t="n">
-        <v>6936636</v>
+        <v>6936643</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,22 +1106,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117448263</v>
+        <v>117447462</v>
       </c>
       <c r="B6" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,25 +1130,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1158,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493988</v>
+        <v>493958</v>
       </c>
       <c r="R6" t="n">
-        <v>6936610</v>
+        <v>6936638</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,22 +1218,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117456705</v>
+        <v>117449604</v>
       </c>
       <c r="B7" t="n">
-        <v>97836</v>
+        <v>79100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,50 +1242,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493873</v>
+        <v>494163</v>
       </c>
       <c r="R7" t="n">
-        <v>6936630</v>
+        <v>6936647</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,18 +1303,27 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1344,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117448979</v>
+        <v>117456679</v>
       </c>
       <c r="B8" t="n">
-        <v>79098</v>
+        <v>97838</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,38 +1354,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494103</v>
+        <v>493840</v>
       </c>
       <c r="R8" t="n">
-        <v>6936656</v>
+        <v>6936658</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,27 +1427,18 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1456,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117456777</v>
+        <v>117451276</v>
       </c>
       <c r="B9" t="n">
-        <v>97836</v>
+        <v>79100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,53 +1469,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493951</v>
+        <v>494282</v>
       </c>
       <c r="R9" t="n">
-        <v>6936605</v>
+        <v>6936738</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1541,40 +1530,49 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117453471</v>
+        <v>117449164</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>78127</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,41 +1581,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493905</v>
+        <v>494158</v>
       </c>
       <c r="R10" t="n">
-        <v>6936651</v>
+        <v>6936645</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1644,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1654,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,22 +1669,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117451454</v>
+        <v>117449658</v>
       </c>
       <c r="B11" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1697,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494251</v>
+        <v>494111</v>
       </c>
       <c r="R11" t="n">
-        <v>6936767</v>
+        <v>6936636</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,22 +1781,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117453528</v>
+        <v>117448979</v>
       </c>
       <c r="B12" t="n">
-        <v>78736</v>
+        <v>79100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,41 +1805,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6459</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493910</v>
+        <v>494103</v>
       </c>
       <c r="R12" t="n">
-        <v>6936649</v>
+        <v>6936656</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1868,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1878,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,22 +1893,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117448702</v>
+        <v>117453471</v>
       </c>
       <c r="B13" t="n">
-        <v>57287</v>
+        <v>79523</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,46 +1917,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493988</v>
+        <v>493905</v>
       </c>
       <c r="R13" t="n">
-        <v>6936610</v>
+        <v>6936651</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1987,7 +1980,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1990,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,22 +2005,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117451276</v>
+        <v>117450152</v>
       </c>
       <c r="B14" t="n">
-        <v>79098</v>
+        <v>77414</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,21 +2033,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,13 +2057,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494282</v>
+        <v>494270</v>
       </c>
       <c r="R14" t="n">
-        <v>6936738</v>
+        <v>6936698</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2099,7 +2092,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2102,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,22 +2117,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117450152</v>
+        <v>117448805</v>
       </c>
       <c r="B15" t="n">
-        <v>77412</v>
+        <v>57288</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,34 +2145,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494270</v>
+        <v>493988</v>
       </c>
       <c r="R15" t="n">
-        <v>6936698</v>
+        <v>6936610</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2211,7 +2209,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2219,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,22 +2234,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117447632</v>
+        <v>117453438</v>
       </c>
       <c r="B16" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,41 +2258,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493952</v>
+        <v>493899</v>
       </c>
       <c r="R16" t="n">
-        <v>6936643</v>
+        <v>6936634</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2323,7 +2321,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2331,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2348,22 +2346,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117449164</v>
+        <v>117456705</v>
       </c>
       <c r="B17" t="n">
-        <v>78125</v>
+        <v>97838</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2372,38 +2370,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494158</v>
+        <v>493873</v>
       </c>
       <c r="R17" t="n">
-        <v>6936645</v>
+        <v>6936630</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,27 +2443,18 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2472,10 +2473,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117449588</v>
+        <v>117448964</v>
       </c>
       <c r="B18" t="n">
-        <v>78125</v>
+        <v>57441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,21 +2489,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2513,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494111</v>
+        <v>494104</v>
       </c>
       <c r="R18" t="n">
-        <v>6936636</v>
+        <v>6936645</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2547,7 +2548,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2558,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2572,22 +2573,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117451261</v>
+        <v>117451640</v>
       </c>
       <c r="B19" t="n">
-        <v>79098</v>
+        <v>90650</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,25 +2597,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2625,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494261</v>
+        <v>494172</v>
       </c>
       <c r="R19" t="n">
-        <v>6936695</v>
+        <v>6936859</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,7 +2660,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2670,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,22 +2685,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117451640</v>
+        <v>117445657</v>
       </c>
       <c r="B20" t="n">
-        <v>90648</v>
+        <v>97838</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,37 +2713,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494172</v>
+        <v>493851</v>
       </c>
       <c r="R20" t="n">
-        <v>6936859</v>
+        <v>6936645</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2771,7 +2781,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2781,7 +2791,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2796,22 +2806,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117453438</v>
+        <v>117448190</v>
       </c>
       <c r="B21" t="n">
-        <v>97836</v>
+        <v>80439</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2820,38 +2830,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493899</v>
+        <v>494007</v>
       </c>
       <c r="R21" t="n">
-        <v>6936634</v>
+        <v>6936619</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2883,7 +2893,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,7 +2903,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2923,7 +2933,7 @@
         <v>117448932</v>
       </c>
       <c r="B22" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3032,10 +3042,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117445550</v>
+        <v>117456777</v>
       </c>
       <c r="B23" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3065,20 +3075,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493843</v>
+        <v>493951</v>
       </c>
       <c r="R23" t="n">
-        <v>6936660</v>
+        <v>6936605</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3105,54 +3127,40 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>15 plantor</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117449528</v>
+        <v>117456532</v>
       </c>
       <c r="B24" t="n">
-        <v>78125</v>
+        <v>97838</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,38 +3169,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494173</v>
+        <v>493986</v>
       </c>
       <c r="R24" t="n">
-        <v>6936639</v>
+        <v>6936667</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3222,39 +3242,30 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3264,7 +3275,7 @@
         <v>117445404</v>
       </c>
       <c r="B25" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3373,10 +3384,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117456809</v>
+        <v>117446108</v>
       </c>
       <c r="B26" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3406,32 +3417,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493939</v>
+        <v>493925</v>
       </c>
       <c r="R26" t="n">
-        <v>6936608</v>
+        <v>6936640</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3458,40 +3457,54 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Fem plantor</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117448964</v>
+        <v>117456480</v>
       </c>
       <c r="B27" t="n">
-        <v>57440</v>
+        <v>97838</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3500,38 +3513,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494104</v>
+        <v>494066</v>
       </c>
       <c r="R27" t="n">
-        <v>6936645</v>
+        <v>6936666</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3561,27 +3586,18 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3600,10 +3616,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117456509</v>
+        <v>117445550</v>
       </c>
       <c r="B28" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3633,32 +3649,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>494062</v>
+        <v>493843</v>
       </c>
       <c r="R28" t="n">
-        <v>6936661</v>
+        <v>6936660</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3685,30 +3689,44 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>15 plantor</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3718,7 +3736,7 @@
         <v>117451670</v>
       </c>
       <c r="B29" t="n">
-        <v>90648</v>
+        <v>90650</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3827,10 +3845,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117456740</v>
+        <v>117451454</v>
       </c>
       <c r="B30" t="n">
-        <v>95384</v>
+        <v>78482</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3843,38 +3861,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>493943</v>
+        <v>494251</v>
       </c>
       <c r="R30" t="n">
-        <v>6936625</v>
+        <v>6936767</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3904,40 +3918,49 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117453330</v>
+        <v>117456588</v>
       </c>
       <c r="B31" t="n">
-        <v>79561</v>
+        <v>78482</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3950,46 +3973,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494077</v>
+        <v>493818</v>
       </c>
       <c r="R31" t="n">
-        <v>6936703</v>
+        <v>6936682</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4016,49 +4033,40 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117447462</v>
+        <v>117446238</v>
       </c>
       <c r="B32" t="n">
-        <v>78480</v>
+        <v>95386</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4071,21 +4079,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4095,10 +4103,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493958</v>
+        <v>493934</v>
       </c>
       <c r="R32" t="n">
-        <v>6936638</v>
+        <v>6936628</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4130,7 +4138,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4140,7 +4148,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4167,10 +4175,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117445657</v>
+        <v>117451854</v>
       </c>
       <c r="B33" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4202,27 +4210,22 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493851</v>
+        <v>494197</v>
       </c>
       <c r="R33" t="n">
-        <v>6936645</v>
+        <v>6936819</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4251,7 +4254,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4261,7 +4264,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4276,22 +4279,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117448190</v>
+        <v>117456550</v>
       </c>
       <c r="B34" t="n">
-        <v>80437</v>
+        <v>97838</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4300,41 +4303,53 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494007</v>
+        <v>493924</v>
       </c>
       <c r="R34" t="n">
-        <v>6936619</v>
+        <v>6936635</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4361,49 +4376,40 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:02</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117448990</v>
+        <v>117450148</v>
       </c>
       <c r="B35" t="n">
-        <v>78217</v>
+        <v>77414</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4416,21 +4422,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4440,10 +4446,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>494108</v>
+        <v>494266</v>
       </c>
       <c r="R35" t="n">
-        <v>6936658</v>
+        <v>6936694</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4475,7 +4481,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4485,7 +4491,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4500,22 +4506,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117456550</v>
+        <v>117456809</v>
       </c>
       <c r="B36" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4547,7 +4553,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4564,10 +4570,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493924</v>
+        <v>493939</v>
       </c>
       <c r="R36" t="n">
-        <v>6936635</v>
+        <v>6936608</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4630,7 +4636,7 @@
         <v>117448642</v>
       </c>
       <c r="B37" t="n">
-        <v>78514</v>
+        <v>78516</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4739,10 +4745,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117446108</v>
+        <v>117451328</v>
       </c>
       <c r="B38" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4751,41 +4757,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>493925</v>
+        <v>494269</v>
       </c>
       <c r="R38" t="n">
-        <v>6936640</v>
+        <v>6936706</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4814,7 +4820,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4824,12 +4830,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Fem plantor</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4844,22 +4845,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117449604</v>
+        <v>117449980</v>
       </c>
       <c r="B39" t="n">
-        <v>79098</v>
+        <v>78516</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4872,21 +4873,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4896,10 +4897,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>494163</v>
+        <v>494241</v>
       </c>
       <c r="R39" t="n">
-        <v>6936647</v>
+        <v>6936727</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4968,10 +4969,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117453136</v>
+        <v>117456450</v>
       </c>
       <c r="B40" t="n">
-        <v>90464</v>
+        <v>97838</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4980,38 +4981,50 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494041</v>
+        <v>494064</v>
       </c>
       <c r="R40" t="n">
-        <v>6936700</v>
+        <v>6936712</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5041,49 +5054,40 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117449980</v>
+        <v>117456509</v>
       </c>
       <c r="B41" t="n">
-        <v>78514</v>
+        <v>97838</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5092,38 +5096,50 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>494241</v>
+        <v>494062</v>
       </c>
       <c r="R41" t="n">
-        <v>6936727</v>
+        <v>6936661</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5153,27 +5169,18 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5192,10 +5199,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117456450</v>
+        <v>117453657</v>
       </c>
       <c r="B42" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5235,19 +5242,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>494064</v>
+        <v>493910</v>
       </c>
       <c r="R42" t="n">
-        <v>6936712</v>
+        <v>6936651</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5277,40 +5281,49 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117456532</v>
+        <v>117448263</v>
       </c>
       <c r="B43" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5340,29 +5353,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493986</v>
+        <v>493988</v>
       </c>
       <c r="R43" t="n">
-        <v>6936667</v>
+        <v>6936610</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5392,40 +5393,49 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117456679</v>
+        <v>117453330</v>
       </c>
       <c r="B44" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5434,53 +5444,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493840</v>
+        <v>494077</v>
       </c>
       <c r="R44" t="n">
-        <v>6936658</v>
+        <v>6936703</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5507,40 +5514,49 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117451854</v>
+        <v>117446539</v>
       </c>
       <c r="B45" t="n">
-        <v>97836</v>
+        <v>91964</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5549,45 +5565,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494197</v>
+        <v>493954</v>
       </c>
       <c r="R45" t="n">
-        <v>6936819</v>
+        <v>6936641</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5616,7 +5628,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5626,7 +5638,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5641,22 +5653,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117453657</v>
+        <v>117448990</v>
       </c>
       <c r="B46" t="n">
-        <v>97836</v>
+        <v>78219</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5665,47 +5677,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493910</v>
+        <v>494108</v>
       </c>
       <c r="R46" t="n">
-        <v>6936651</v>
+        <v>6936658</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5737,7 +5740,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5747,7 +5750,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5762,22 +5765,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117451328</v>
+        <v>117453528</v>
       </c>
       <c r="B47" t="n">
-        <v>78480</v>
+        <v>78738</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5786,41 +5789,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>494269</v>
+        <v>493910</v>
       </c>
       <c r="R47" t="n">
-        <v>6936706</v>
+        <v>6936649</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5849,7 +5852,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5859,7 +5862,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5874,22 +5877,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117446238</v>
+        <v>117453136</v>
       </c>
       <c r="B48" t="n">
-        <v>95384</v>
+        <v>90466</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5898,41 +5901,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493934</v>
+        <v>494041</v>
       </c>
       <c r="R48" t="n">
-        <v>6936628</v>
+        <v>6936700</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5961,7 +5964,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5971,7 +5974,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5998,10 +6001,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117446539</v>
+        <v>117449588</v>
       </c>
       <c r="B49" t="n">
-        <v>91962</v>
+        <v>78127</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6014,21 +6017,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6038,13 +6041,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493954</v>
+        <v>494111</v>
       </c>
       <c r="R49" t="n">
-        <v>6936641</v>
+        <v>6936636</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6073,7 +6076,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6083,7 +6086,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6098,22 +6101,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117456480</v>
+        <v>117445529</v>
       </c>
       <c r="B50" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6122,53 +6125,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Guckflon (Guckflon), Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>494066</v>
+        <v>493855</v>
       </c>
       <c r="R50" t="n">
-        <v>6936666</v>
+        <v>6936651</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6195,30 +6186,39 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6228,7 +6228,7 @@
         <v>117487483</v>
       </c>
       <c r="B51" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6332,10 +6332,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117505814</v>
+        <v>117506039</v>
       </c>
       <c r="B52" t="n">
-        <v>95384</v>
+        <v>79563</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6348,27 +6348,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6376,13 +6375,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493952</v>
+        <v>493988</v>
       </c>
       <c r="R52" t="n">
-        <v>6936632</v>
+        <v>6936642</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6439,10 +6438,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117506039</v>
+        <v>117506518</v>
       </c>
       <c r="B53" t="n">
-        <v>79561</v>
+        <v>79100</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6455,21 +6454,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6482,13 +6481,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493988</v>
+        <v>494188</v>
       </c>
       <c r="R53" t="n">
-        <v>6936642</v>
+        <v>6936650</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6545,10 +6544,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117506518</v>
+        <v>117506348</v>
       </c>
       <c r="B54" t="n">
-        <v>79098</v>
+        <v>90650</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6557,25 +6556,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6588,10 +6587,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494188</v>
+        <v>494153</v>
       </c>
       <c r="R54" t="n">
-        <v>6936650</v>
+        <v>6936771</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6651,10 +6650,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117506348</v>
+        <v>117505814</v>
       </c>
       <c r="B55" t="n">
-        <v>90648</v>
+        <v>95386</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6663,30 +6662,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6694,10 +6694,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494153</v>
+        <v>493952</v>
       </c>
       <c r="R55" t="n">
-        <v>6936771</v>
+        <v>6936632</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6760,7 +6760,7 @@
         <v>117734552</v>
       </c>
       <c r="B56" t="n">
-        <v>56499</v>
+        <v>56500</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>117734554</v>
       </c>
       <c r="B57" t="n">
-        <v>57440</v>
+        <v>57441</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>

--- a/artfynd/A 20269-2024 artfynd.xlsx
+++ b/artfynd/A 20269-2024 artfynd.xlsx
@@ -2132,7 +2132,7 @@
         <v>117448805</v>
       </c>
       <c r="B15" t="n">
-        <v>57288</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Guckflon (Guckflon), Jmt</t>
+          <t>Guckflon, Guckflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">

--- a/artfynd/A 20269-2024 artfynd.xlsx
+++ b/artfynd/A 20269-2024 artfynd.xlsx
@@ -2132,7 +2132,7 @@
         <v>117448805</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 20269-2024 artfynd.xlsx
+++ b/artfynd/A 20269-2024 artfynd.xlsx
@@ -2132,7 +2132,7 @@
         <v>117448805</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 20269-2024 artfynd.xlsx
+++ b/artfynd/A 20269-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117446238</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117456740</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117505814</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117448642</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117449980</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117453005</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117453012</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117449164</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117449528</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117449588</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1839,6 +1894,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117448190</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117451640</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2053,6 +2118,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117451670</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2154,6 +2224,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117506348</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2261,6 +2336,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117446539</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2368,6 +2448,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117720528</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2475,6 +2560,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117453084</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2582,6 +2672,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117453136</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2689,6 +2784,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117445529</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2796,6 +2896,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117447462</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2903,6 +3008,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117447632</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3010,6 +3120,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117448932</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3117,6 +3232,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117451328</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3224,6 +3344,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117451454</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3325,6 +3450,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117456588</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3432,6 +3562,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117448979</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3539,6 +3674,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117449604</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3646,6 +3786,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117449658</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3753,6 +3898,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117451261</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3860,6 +4010,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117451276</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3961,6 +4116,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117506518</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4068,6 +4228,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117447790</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4184,6 +4349,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117453330</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4285,6 +4455,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117506039</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4392,6 +4567,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117453528</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4499,6 +4679,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117447823</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4606,6 +4791,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117450148</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4713,6 +4903,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117450152</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4825,6 +5020,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117448702</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4930,6 +5130,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117734552</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5037,6 +5242,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117448964</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5142,6 +5352,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117734554</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5249,6 +5464,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117445404</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5361,6 +5581,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117445550</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5477,6 +5702,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117445657</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5589,6 +5819,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117446108</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5696,6 +5931,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117448263</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5812,6 +6052,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117451838</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5923,6 +6168,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117451854</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6039,6 +6289,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117452612</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6146,6 +6401,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117453438</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6262,6 +6522,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117453657</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6372,6 +6637,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117456450</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6482,6 +6752,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117456480</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6592,6 +6867,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117456509</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6702,6 +6982,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117456532</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6812,6 +7097,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117456550</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6922,6 +7212,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117456679</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7032,6 +7327,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117456705</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7142,6 +7442,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117456777</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7252,6 +7557,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117456809</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7354,6 +7664,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117487278</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7461,6 +7776,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117448990</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7568,8 +7888,79 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117453471</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>